--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2023_valparaiso.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2023_valparaiso.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:59</t>
+    <t xml:space="preserve">2026-09-24 01:48</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -875,13 +875,13 @@
         <v>27</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>-0.26</v>
+        <v>-0.14</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-0.08</v>
+        <v>-0.04</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>-0.18</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="16">
@@ -898,13 +898,13 @@
         <v>27</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>-0.21</v>
+        <v>-0.12</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-0.24</v>
+        <v>-0.16</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="17">
@@ -921,13 +921,13 @@
         <v>27</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>-0.27</v>
+        <v>-0.09</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>-0.42</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="18">
@@ -1266,13 +1266,13 @@
         <v>27</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>-0.26</v>
+        <v>-0.13</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>-0.08</v>
+        <v>-0.04</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>-0.18</v>
+        <v>-0.09</v>
       </c>
     </row>
     <row r="33">
@@ -1289,13 +1289,13 @@
         <v>27</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>-0.21</v>
+        <v>-0.11</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>-0.23</v>
+        <v>-0.15</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="34">
@@ -1312,13 +1312,13 @@
         <v>27</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>-0.27</v>
+        <v>-0.08</v>
       </c>
       <c r="F34" s="2" t="n">
         <v>0.15</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>-0.42</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="35">
@@ -1657,13 +1657,13 @@
         <v>27</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>-0.59</v>
+        <v>-0.29</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>-0.54</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="50">
@@ -1680,13 +1680,13 @@
         <v>27</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>-0.61</v>
+        <v>-0.52</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>-0.48</v>
+        <v>-0.42</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>-0.13</v>
+        <v>-0.09</v>
       </c>
     </row>
     <row r="51">
@@ -1703,13 +1703,13 @@
         <v>27</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>-0.42</v>
+        <v>-0.22</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>0.24</v>
+        <v>0.26</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>-0.65</v>
+        <v>-0.48</v>
       </c>
     </row>
     <row r="52">
@@ -2048,13 +2048,13 @@
         <v>27</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>-0.56</v>
+        <v>-0.27</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>-0.06</v>
+        <v>-0.07</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>-0.51</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="67">
@@ -2071,13 +2071,13 @@
         <v>27</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>-0.57</v>
+        <v>-0.48</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>-0.43</v>
+        <v>-0.38</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>-0.14</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="68">
@@ -2094,13 +2094,13 @@
         <v>27</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>-0.4</v>
+        <v>-0.22</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>0.19</v>
+        <v>0.23</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>-0.6</v>
+        <v>-0.44</v>
       </c>
     </row>
     <row r="69">
@@ -2439,13 +2439,13 @@
         <v>27</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>-0.38</v>
+        <v>-0.12</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>0.09</v>
+        <v>0.18</v>
       </c>
       <c r="G83" s="2" t="n">
-        <v>-0.47</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="84">
@@ -2462,13 +2462,13 @@
         <v>27</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>-0.34</v>
+        <v>-0.2</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>-0.32</v>
+        <v>-0.22</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>-0.02</v>
+        <v>0.02</v>
       </c>
     </row>
     <row r="85">
@@ -2485,13 +2485,13 @@
         <v>27</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>-0.35</v>
+        <v>-0.11</v>
       </c>
       <c r="F85" s="2" t="n">
-        <v>0.22</v>
+        <v>0.25</v>
       </c>
       <c r="G85" s="2" t="n">
-        <v>-0.57</v>
+        <v>-0.36</v>
       </c>
     </row>
     <row r="86">
@@ -2830,13 +2830,13 @@
         <v>27</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>-0.22</v>
+        <v>-0.01</v>
       </c>
       <c r="F100" s="2" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="G100" s="2" t="n">
-        <v>-0.24</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="101">
@@ -2853,13 +2853,13 @@
         <v>27</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>-0.17</v>
+        <v>-0.05</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>-0.22</v>
+        <v>-0.15</v>
       </c>
       <c r="G101" s="2" t="n">
-        <v>0.05</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="102">
@@ -2876,13 +2876,13 @@
         <v>27</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>-0.26</v>
+        <v>-0.13</v>
       </c>
       <c r="F102" s="2" t="n">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="G102" s="2" t="n">
-        <v>-0.34</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="103">
@@ -3221,13 +3221,13 @@
         <v>27</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>-0.21</v>
+        <v>-0.12</v>
       </c>
       <c r="F117" s="2" t="n">
-        <v>-0.16</v>
+        <v>-0.06</v>
       </c>
       <c r="G117" s="2" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="118">
@@ -3244,13 +3244,13 @@
         <v>27</v>
       </c>
       <c r="E118" s="2" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F118" s="2" t="n">
         <v>0.11</v>
       </c>
-      <c r="F118" s="2" t="n">
-        <v>0.15</v>
-      </c>
       <c r="G118" s="2" t="n">
-        <v>-0.04</v>
+        <v>-0.09</v>
       </c>
     </row>
     <row r="119">
@@ -3267,13 +3267,13 @@
         <v>27</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>-0.05</v>
+        <v>0</v>
       </c>
       <c r="F119" s="2" t="n">
-        <v>-0.02</v>
+        <v>0.06</v>
       </c>
       <c r="G119" s="2" t="n">
-        <v>-0.03</v>
+        <v>-0.06</v>
       </c>
     </row>
     <row r="120">
@@ -3612,10 +3612,10 @@
         <v>27</v>
       </c>
       <c r="E134" s="2" t="n">
-        <v>-0.38</v>
+        <v>-0.28</v>
       </c>
       <c r="F134" s="2" t="n">
-        <v>-0.32</v>
+        <v>-0.21</v>
       </c>
       <c r="G134" s="2" t="n">
         <v>-0.06</v>
@@ -3635,13 +3635,13 @@
         <v>27</v>
       </c>
       <c r="E135" s="2" t="n">
-        <v>0.06</v>
+        <v>-0.08</v>
       </c>
       <c r="F135" s="2" t="n">
-        <v>0.23</v>
+        <v>0.14</v>
       </c>
       <c r="G135" s="2" t="n">
-        <v>-0.16</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="136">
@@ -3658,13 +3658,13 @@
         <v>27</v>
       </c>
       <c r="E136" s="2" t="n">
-        <v>-0.21</v>
+        <v>-0.14</v>
       </c>
       <c r="F136" s="2" t="n">
-        <v>-0.14</v>
+        <v>-0.1</v>
       </c>
       <c r="G136" s="2" t="n">
-        <v>-0.07</v>
+        <v>-0.03</v>
       </c>
     </row>
     <row r="137">

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2023_valparaiso.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2023_valparaiso.xlsx
@@ -102,7 +102,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:48</t>
+    <t xml:space="preserve">2026-10-01 23:22</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2023_valparaiso.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_matricula_a_2023_valparaiso.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:22</t>
+    <t xml:space="preserve">2026-10-05 20:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
